--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_5.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_5.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\joyin\workspace\BS-1.9\dev\branches\2.1.2\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HSbank_branches20201013\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7770"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
   </bookViews>
   <sheets>
     <sheet name="表1-5提前及延期兑付" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -37,9 +37,6 @@
   </si>
   <si>
     <t>产品品种：</t>
-  </si>
-  <si>
-    <t>单位：万元，只</t>
   </si>
   <si>
     <t>列编号</t>
@@ -187,6 +184,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>其中：收益权转让产品</t>
@@ -911,6 +909,10 @@
   </si>
   <si>
     <t xml:space="preserve">  产品类型</t>
+  </si>
+  <si>
+    <t>单位：万元，只</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -925,7 +927,7 @@
     <numFmt numFmtId="180" formatCode="0_ "/>
     <numFmt numFmtId="181" formatCode="#,##0.000000_ "/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -937,32 +939,38 @@
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10.5"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -974,6 +982,7 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -984,11 +993,13 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -997,6 +1008,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1251,61 +1270,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1618,19 +1637,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
     </row>
     <row r="2" spans="1:11" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
@@ -1641,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="3"/>
@@ -1655,33 +1674,33 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="55" t="s">
-        <v>240</v>
-      </c>
-      <c r="G3" s="56"/>
+      <c r="F3" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="G3" s="54"/>
       <c r="H3" s="3"/>
       <c r="I3" s="10"/>
       <c r="J3" s="11" t="s">
         <v>4</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="6" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="57" t="s">
-        <v>245</v>
-      </c>
-      <c r="C4" s="57"/>
+      <c r="B4" s="55" t="s">
+        <v>244</v>
+      </c>
+      <c r="C4" s="55"/>
       <c r="D4" s="46"/>
       <c r="E4" s="47"/>
       <c r="F4" s="47"/>
@@ -1690,148 +1709,148 @@
       <c r="I4" s="50"/>
       <c r="J4" s="50"/>
       <c r="K4" s="51" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="6" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A5" s="43"/>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="56"/>
+      <c r="D5" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="44" t="s">
+      <c r="E5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="F5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="G5" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="44" t="s">
+      <c r="H5" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="I5" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="44" t="s">
+      <c r="J5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="K5" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="44" t="s">
+    </row>
+    <row r="6" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A6" s="57" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="59" t="s">
+      <c r="B6" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="60" t="s">
+      <c r="C6" s="58"/>
+      <c r="D6" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="60"/>
-      <c r="D6" s="61" t="s">
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="61" t="s">
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+    </row>
+    <row r="7" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A7" s="57"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="63"/>
-    </row>
-    <row r="7" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A7" s="59"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60" t="s">
+      <c r="E7" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="65"/>
+      <c r="K7" s="65"/>
+    </row>
+    <row r="8" spans="1:11" s="14" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A8" s="57"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="68" t="s">
+      <c r="F8" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="64"/>
+      <c r="I8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-    </row>
-    <row r="8" spans="1:11" s="14" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A8" s="59"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="12" t="s">
+      <c r="J8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="K8" s="13" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="67"/>
-      <c r="I8" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="15" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A9" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="B9" s="69" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="69"/>
+        <v>245</v>
+      </c>
+      <c r="B9" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="66"/>
       <c r="D9" s="35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F9" s="36" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G9" s="36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I9" s="36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J9" s="36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K9" s="36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A10" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="B10" s="69" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="69"/>
+        <v>246</v>
+      </c>
+      <c r="B10" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="66"/>
       <c r="D10" s="16"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17"/>
@@ -1843,186 +1862,186 @@
     </row>
     <row r="11" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A11" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="B11" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="52"/>
+        <v>247</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="63"/>
       <c r="D11" s="16"/>
       <c r="E11" s="36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G11" s="36" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H11" s="16"/>
       <c r="I11" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J11" s="36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K11" s="36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A12" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="B12" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="52"/>
+        <v>248</v>
+      </c>
+      <c r="B12" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="63"/>
       <c r="D12" s="16"/>
       <c r="E12" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H12" s="16"/>
       <c r="I12" s="36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J12" s="36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K12" s="36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A13" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="B13" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="52"/>
+        <v>249</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="63"/>
       <c r="D13" s="16"/>
       <c r="E13" s="36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G13" s="36" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J13" s="36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K13" s="36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A14" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="B14" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="52"/>
+        <v>250</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="63"/>
       <c r="D14" s="16"/>
       <c r="E14" s="36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J14" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K14" s="36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A15" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="B15" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="52"/>
+        <v>251</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="63"/>
       <c r="D15" s="16"/>
       <c r="E15" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A16" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="B16" s="52" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="52"/>
+        <v>252</v>
+      </c>
+      <c r="B16" s="63" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="63"/>
       <c r="D16" s="16"/>
       <c r="E16" s="36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G16" s="36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J16" s="36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K16" s="36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="19" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A17" s="34" t="s">
-        <v>254</v>
-      </c>
-      <c r="B17" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="53"/>
+        <v>253</v>
+      </c>
+      <c r="B17" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="67"/>
       <c r="D17" s="16"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
@@ -2034,144 +2053,144 @@
     </row>
     <row r="18" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A18" s="34" t="s">
-        <v>255</v>
-      </c>
-      <c r="B18" s="52" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="52"/>
+        <v>254</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="63"/>
       <c r="D18" s="35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G18" s="36" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H18" s="35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J18" s="36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K18" s="36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A19" s="34" t="s">
-        <v>257</v>
-      </c>
-      <c r="B19" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="52"/>
+        <v>256</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="63"/>
       <c r="D19" s="35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G19" s="36" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H19" s="35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J19" s="36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K19" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A20" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="B20" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="52"/>
+        <v>257</v>
+      </c>
+      <c r="B20" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="63"/>
       <c r="D20" s="35" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G20" s="36" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H20" s="35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I20" s="36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A21" s="34" t="s">
-        <v>259</v>
-      </c>
-      <c r="B21" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="52"/>
+        <v>258</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="63"/>
       <c r="D21" s="35" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G21" s="36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H21" s="35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I21" s="36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J21" s="36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K21" s="36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A22" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="B22" s="69" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="69"/>
+        <v>259</v>
+      </c>
+      <c r="B22" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="66"/>
       <c r="D22" s="16"/>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
@@ -2183,78 +2202,78 @@
     </row>
     <row r="23" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A23" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="B23" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="52"/>
+        <v>260</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="63"/>
       <c r="D23" s="35" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G23" s="36" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H23" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I23" s="36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J23" s="36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K23" s="36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A24" s="34" t="s">
-        <v>265</v>
-      </c>
-      <c r="B24" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="52"/>
+        <v>264</v>
+      </c>
+      <c r="B24" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="63"/>
       <c r="D24" s="35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H24" s="35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J24" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K24" s="36" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A25" s="34" t="s">
-        <v>256</v>
-      </c>
-      <c r="B25" s="65" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="65"/>
+        <v>255</v>
+      </c>
+      <c r="B25" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="69"/>
       <c r="D25" s="16"/>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
@@ -2266,78 +2285,78 @@
     </row>
     <row r="26" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A26" s="34" t="s">
-        <v>262</v>
-      </c>
-      <c r="B26" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="66"/>
+        <v>261</v>
+      </c>
+      <c r="B26" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="68"/>
       <c r="D26" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G26" s="36" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H26" s="35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I26" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J26" s="36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K26" s="36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A27" s="34" t="s">
-        <v>263</v>
-      </c>
-      <c r="B27" s="66" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="66"/>
+        <v>262</v>
+      </c>
+      <c r="B27" s="68" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="68"/>
       <c r="D27" s="35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F27" s="36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G27" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H27" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I27" s="36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J27" s="36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K27" s="36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A28" s="34" t="s">
-        <v>264</v>
-      </c>
-      <c r="B28" s="65" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="65"/>
+        <v>263</v>
+      </c>
+      <c r="B28" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="69"/>
       <c r="D28" s="16"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
@@ -2349,76 +2368,76 @@
     </row>
     <row r="29" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A29" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="B29" s="66" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="66"/>
+        <v>265</v>
+      </c>
+      <c r="B29" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="68"/>
       <c r="D29" s="35" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F29" s="36" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G29" s="36" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H29" s="35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I29" s="36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J29" s="36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K29" s="36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A30" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="B30" s="66" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="66"/>
+        <v>266</v>
+      </c>
+      <c r="B30" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="68"/>
       <c r="D30" s="35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G30" s="36" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I30" s="36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J30" s="36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K30" s="36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A31" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B31" s="73" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C31" s="73"/>
       <c r="D31" s="16"/>
@@ -2432,144 +2451,144 @@
     </row>
     <row r="32" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A32" s="34" t="s">
-        <v>269</v>
-      </c>
-      <c r="B32" s="66" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="66"/>
+        <v>268</v>
+      </c>
+      <c r="B32" s="68" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="68"/>
       <c r="D32" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G32" s="36" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H32" s="35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I32" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J32" s="36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K32" s="36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A33" s="34" t="s">
-        <v>270</v>
-      </c>
-      <c r="B33" s="66" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="66"/>
+        <v>269</v>
+      </c>
+      <c r="B33" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="68"/>
       <c r="D33" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H33" s="35" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A34" s="34" t="s">
-        <v>271</v>
-      </c>
-      <c r="B34" s="66" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="66"/>
+        <v>270</v>
+      </c>
+      <c r="B34" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="68"/>
       <c r="D34" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G34" s="36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H34" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I34" s="36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J34" s="36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K34" s="36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A35" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="B35" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="66"/>
+        <v>271</v>
+      </c>
+      <c r="B35" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="68"/>
       <c r="D35" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G35" s="36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H35" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I35" s="36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J35" s="36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K35" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A36" s="34" t="s">
-        <v>273</v>
-      </c>
-      <c r="B36" s="65" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="65"/>
+        <v>272</v>
+      </c>
+      <c r="B36" s="69" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="69"/>
       <c r="D36" s="37"/>
       <c r="E36" s="38"/>
       <c r="F36" s="39"/>
@@ -2581,106 +2600,106 @@
     </row>
     <row r="37" spans="1:11" s="7" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="34" t="s">
-        <v>274</v>
-      </c>
-      <c r="B37" s="66" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="66"/>
+        <v>273</v>
+      </c>
+      <c r="B37" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="68"/>
       <c r="D37" s="20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G37" s="36" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I37" s="36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J37" s="36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K37" s="36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="34" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B38" s="70" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="66"/>
+        <v>52</v>
+      </c>
+      <c r="C38" s="68"/>
       <c r="D38" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G38" s="36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H38" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I38" s="36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J38" s="36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K38" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="7" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A39" s="40" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B39" s="71" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C39" s="71"/>
       <c r="D39" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G39" s="41" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H39" s="42" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I39" s="41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J39" s="41" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K39" s="41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="7" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="72" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B40" s="72"/>
       <c r="C40" s="72"/>
@@ -2695,27 +2714,27 @@
     </row>
     <row r="41" spans="1:11" s="30" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C41" s="25"/>
       <c r="D41" s="23"/>
       <c r="E41" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F41" s="23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G41" s="27"/>
       <c r="H41" s="28"/>
       <c r="I41" s="29"/>
       <c r="J41" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_5.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_5.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HSbank_branches20201013\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\ZGBS-CP\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D899A198-5C78-489D-BCCA-C39AFB0F017A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表1-5提前及延期兑付" sheetId="1" r:id="rId1"/>
@@ -191,9 +192,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">    其中：货币市场基金</t>
-  </si>
-  <si>
     <t xml:space="preserve">注：1.通过下拉选项选择。
     2.各币种折人民币汇率使用报告期最后一个交易日外汇局公布的各币种折人民币汇率中间价。
     3.如果1只产品募集金额既有人民币又有外币，则只数计1只。 
@@ -914,11 +912,15 @@
     <t>单位：万元，只</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">    其中：货币市场基金或现金管理类产品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
@@ -1273,6 +1275,39 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1305,45 +1340,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
-    <cellStyle name="常规_demo-交叉报表（列标题分为2级）" xfId="2"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规_demo-交叉报表（列标题分为2级）" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1620,38 +1622,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K42"/>
-  <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.399999999999999" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.625" style="31" customWidth="1"/>
-    <col min="2" max="2" width="8.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.625" style="32" customWidth="1"/>
-    <col min="4" max="4" width="12.125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="12.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="33" customWidth="1"/>
-    <col min="7" max="9" width="12.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" style="31" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" style="32" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="32" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="33" customWidth="1"/>
+    <col min="7" max="9" width="12.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="52" t="s">
+    <row r="1" spans="1:11" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-    </row>
-    <row r="2" spans="1:11" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+    </row>
+    <row r="2" spans="1:11" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1660,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="3"/>
@@ -1668,39 +1670,39 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="53" t="s">
-        <v>239</v>
-      </c>
-      <c r="G3" s="54"/>
+      <c r="F3" s="64" t="s">
+        <v>238</v>
+      </c>
+      <c r="G3" s="65"/>
       <c r="H3" s="3"/>
       <c r="I3" s="10"/>
       <c r="J3" s="11" t="s">
         <v>4</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="6" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="6" customFormat="1" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="55" t="s">
-        <v>244</v>
-      </c>
-      <c r="C4" s="55"/>
+      <c r="B4" s="66" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4" s="66"/>
       <c r="D4" s="46"/>
       <c r="E4" s="47"/>
       <c r="F4" s="47"/>
@@ -1709,15 +1711,15 @@
       <c r="I4" s="50"/>
       <c r="J4" s="50"/>
       <c r="K4" s="51" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="6" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A5" s="43"/>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="56"/>
+      <c r="C5" s="67"/>
       <c r="D5" s="44" t="s">
         <v>7</v>
       </c>
@@ -1743,53 +1745,53 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="57" t="s">
+    <row r="6" spans="1:11" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="59" t="s">
+      <c r="C6" s="69"/>
+      <c r="D6" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="59" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-    </row>
-    <row r="7" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A7" s="57"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58" t="s">
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+    </row>
+    <row r="7" spans="1:11" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="68"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="64" t="s">
+      <c r="F7" s="73"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="65" t="s">
+      <c r="I7" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="65"/>
-      <c r="K7" s="65"/>
-    </row>
-    <row r="8" spans="1:11" s="14" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+    </row>
+    <row r="8" spans="1:11" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A8" s="68"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
       <c r="E8" s="12" t="s">
         <v>21</v>
       </c>
@@ -1799,7 +1801,7 @@
       <c r="G8" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="64"/>
+      <c r="H8" s="60"/>
       <c r="I8" s="12" t="s">
         <v>21</v>
       </c>
@@ -1810,47 +1812,47 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="15" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" s="15" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="59"/>
+      <c r="D9" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="F9" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="G9" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="I9" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="36" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="B9" s="66" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="G9" s="36" t="s">
-        <v>214</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="K9" s="36" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A10" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="66"/>
+      <c r="C10" s="59"/>
       <c r="D10" s="16"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17"/>
@@ -1860,188 +1862,188 @@
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
     </row>
-    <row r="11" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="B11" s="63" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="63"/>
+      <c r="C11" s="58"/>
       <c r="D11" s="16"/>
       <c r="E11" s="36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G11" s="36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H11" s="16"/>
       <c r="I11" s="36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J11" s="36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K11" s="36" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="B12" s="63" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="63"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="16"/>
       <c r="E12" s="36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H12" s="16"/>
       <c r="I12" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J12" s="36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K12" s="36" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="B13" s="63" t="s">
+        <v>248</v>
+      </c>
+      <c r="B13" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="63"/>
+      <c r="C13" s="58"/>
       <c r="D13" s="16"/>
       <c r="E13" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G13" s="36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J13" s="36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K13" s="36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="B14" s="63" t="s">
+        <v>249</v>
+      </c>
+      <c r="B14" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="63"/>
+      <c r="C14" s="58"/>
       <c r="D14" s="16"/>
       <c r="E14" s="36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J14" s="36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K14" s="36" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="B15" s="63" t="s">
+        <v>250</v>
+      </c>
+      <c r="B15" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="63"/>
+      <c r="C15" s="58"/>
       <c r="D15" s="16"/>
       <c r="E15" s="36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="B16" s="63" t="s">
+        <v>251</v>
+      </c>
+      <c r="B16" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="63"/>
+      <c r="C16" s="58"/>
       <c r="D16" s="16"/>
       <c r="E16" s="36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G16" s="36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J16" s="36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K16" s="36" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="19" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="19" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="B17" s="67" t="s">
+        <v>252</v>
+      </c>
+      <c r="B17" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="67"/>
+      <c r="C17" s="62"/>
       <c r="D17" s="16"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
@@ -2051,146 +2053,146 @@
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
     </row>
-    <row r="18" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
-        <v>254</v>
-      </c>
-      <c r="B18" s="63" t="s">
+        <v>253</v>
+      </c>
+      <c r="B18" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="63"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="F18" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="G18" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="I18" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="J18" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="K18" s="36" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A19" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="58"/>
+      <c r="D19" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E19" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F19" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="G18" s="36" t="s">
+      <c r="G19" s="36" t="s">
         <v>221</v>
       </c>
-      <c r="H18" s="35" t="s">
+      <c r="H19" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="I18" s="36" t="s">
+      <c r="I19" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="J18" s="36" t="s">
+      <c r="J19" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="K18" s="36" t="s">
+      <c r="K19" s="36" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A19" s="34" t="s">
+    <row r="20" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="B19" s="63" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="63"/>
-      <c r="D19" s="35" t="s">
+      <c r="B20" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="58"/>
+      <c r="D20" s="35" t="s">
         <v>174</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E20" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F20" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="G19" s="36" t="s">
+      <c r="G20" s="36" t="s">
         <v>222</v>
       </c>
-      <c r="H19" s="35" t="s">
+      <c r="H20" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="I19" s="36" t="s">
+      <c r="I20" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="J19" s="36" t="s">
+      <c r="J20" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="K19" s="36" t="s">
+      <c r="K20" s="36" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A20" s="34" t="s">
+    <row r="21" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A21" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="B20" s="63" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="63"/>
-      <c r="D20" s="35" t="s">
+      <c r="B21" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="58"/>
+      <c r="D21" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E21" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="F20" s="36" t="s">
+      <c r="F21" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="G20" s="36" t="s">
+      <c r="G21" s="36" t="s">
         <v>223</v>
       </c>
-      <c r="H20" s="35" t="s">
+      <c r="H21" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="I20" s="36" t="s">
+      <c r="I21" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="J20" s="36" t="s">
+      <c r="J21" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="K20" s="36" t="s">
+      <c r="K21" s="36" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A21" s="34" t="s">
+    <row r="22" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A22" s="34" t="s">
         <v>258</v>
       </c>
-      <c r="B21" s="63" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="63"/>
-      <c r="D21" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="F21" s="36" t="s">
-        <v>200</v>
-      </c>
-      <c r="G21" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="I21" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="J21" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="K21" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A22" s="34" t="s">
-        <v>259</v>
-      </c>
-      <c r="B22" s="66" t="s">
+      <c r="B22" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="66"/>
+      <c r="C22" s="59"/>
       <c r="D22" s="16"/>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
@@ -2200,80 +2202,80 @@
       <c r="J22" s="17"/>
       <c r="K22" s="17"/>
     </row>
-    <row r="23" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="B23" s="63" t="s">
+        <v>259</v>
+      </c>
+      <c r="B23" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="63"/>
+      <c r="C23" s="58"/>
       <c r="D23" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="F23" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="G23" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="H23" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="I23" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="J23" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="K23" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A24" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="B24" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="58"/>
+      <c r="D24" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="E23" s="36" t="s">
+      <c r="E24" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F24" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="G23" s="36" t="s">
+      <c r="G24" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="H23" s="35" t="s">
+      <c r="H24" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="I23" s="36" t="s">
+      <c r="I24" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="J23" s="36" t="s">
+      <c r="J24" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="K23" s="36" t="s">
+      <c r="K24" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A24" s="34" t="s">
-        <v>264</v>
-      </c>
-      <c r="B24" s="63" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="63"/>
-      <c r="D24" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="F24" s="36" t="s">
-        <v>202</v>
-      </c>
-      <c r="G24" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="H24" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="J24" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="K24" s="36" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>255</v>
-      </c>
-      <c r="B25" s="69" t="s">
+        <v>254</v>
+      </c>
+      <c r="B25" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="69"/>
+      <c r="C25" s="57"/>
       <c r="D25" s="16"/>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
@@ -2283,80 +2285,80 @@
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="B26" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="52"/>
+      <c r="D26" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="F26" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="G26" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="H26" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="I26" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J26" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="K26" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="18" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A27" s="34" t="s">
         <v>261</v>
       </c>
-      <c r="B26" s="68" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="68"/>
-      <c r="D26" s="35" t="s">
+      <c r="B27" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="52"/>
+      <c r="D27" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="E26" s="36" t="s">
+      <c r="E27" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="F26" s="36" t="s">
+      <c r="F27" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="G26" s="36" t="s">
+      <c r="G27" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="H26" s="35" t="s">
+      <c r="H27" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="I26" s="36" t="s">
+      <c r="I27" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="J26" s="36" t="s">
+      <c r="J27" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="K26" s="36" t="s">
+      <c r="K27" s="36" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A27" s="34" t="s">
+    <row r="28" spans="1:11" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A28" s="34" t="s">
         <v>262</v>
       </c>
-      <c r="B27" s="68" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="68"/>
-      <c r="D27" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="F27" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="G27" s="36" t="s">
-        <v>228</v>
-      </c>
-      <c r="H27" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="I27" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="J27" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="K27" s="36" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A28" s="34" t="s">
-        <v>263</v>
-      </c>
-      <c r="B28" s="69" t="s">
+      <c r="B28" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="69"/>
+      <c r="C28" s="57"/>
       <c r="D28" s="16"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
@@ -2366,80 +2368,80 @@
       <c r="J28" s="17"/>
       <c r="K28" s="17"/>
     </row>
-    <row r="29" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:11" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A29" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="B29" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="52"/>
+      <c r="D29" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="F29" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="G29" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="H29" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="I29" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="J29" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="K29" s="36" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A30" s="34" t="s">
         <v>265</v>
       </c>
-      <c r="B29" s="68" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="35" t="s">
+      <c r="B30" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="52"/>
+      <c r="D30" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="E29" s="36" t="s">
+      <c r="E30" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="F29" s="36" t="s">
+      <c r="F30" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="G29" s="36" t="s">
+      <c r="G30" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="H29" s="35" t="s">
+      <c r="H30" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="I29" s="36" t="s">
+      <c r="I30" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="J29" s="36" t="s">
+      <c r="J30" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="K29" s="36" t="s">
+      <c r="K30" s="36" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A30" s="34" t="s">
+    <row r="31" spans="1:11" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A31" s="34" t="s">
         <v>266</v>
       </c>
-      <c r="B30" s="68" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="68"/>
-      <c r="D30" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="F30" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="G30" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="H30" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="I30" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="J30" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="K30" s="36" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A31" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="B31" s="73" t="s">
-        <v>277</v>
-      </c>
-      <c r="C31" s="73"/>
+      <c r="B31" s="56" t="s">
+        <v>276</v>
+      </c>
+      <c r="C31" s="56"/>
       <c r="D31" s="16"/>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
@@ -2449,146 +2451,146 @@
       <c r="J31" s="17"/>
       <c r="K31" s="17"/>
     </row>
-    <row r="32" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:11" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="B32" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="52"/>
+      <c r="D32" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="G32" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="H32" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="I32" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="J32" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="K32" s="36" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="B32" s="68" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="68"/>
-      <c r="D32" s="35" t="s">
+      <c r="B33" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="52"/>
+      <c r="D33" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="E32" s="36" t="s">
+      <c r="E33" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="F32" s="36" t="s">
+      <c r="F33" s="36" t="s">
         <v>207</v>
       </c>
-      <c r="G32" s="36" t="s">
+      <c r="G33" s="36" t="s">
         <v>231</v>
       </c>
-      <c r="H32" s="35" t="s">
+      <c r="H33" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="I32" s="36" t="s">
+      <c r="I33" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="J32" s="36" t="s">
+      <c r="J33" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="K32" s="36" t="s">
+      <c r="K33" s="36" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A33" s="34" t="s">
+    <row r="34" spans="1:11" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A34" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="B33" s="68" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="68"/>
-      <c r="D33" s="35" t="s">
+      <c r="B34" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="52"/>
+      <c r="D34" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="E33" s="36" t="s">
+      <c r="E34" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="F33" s="36" t="s">
+      <c r="F34" s="36" t="s">
         <v>208</v>
       </c>
-      <c r="G33" s="36" t="s">
+      <c r="G34" s="36" t="s">
         <v>232</v>
       </c>
-      <c r="H33" s="35" t="s">
+      <c r="H34" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="I33" s="36" t="s">
+      <c r="I34" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="J33" s="36" t="s">
+      <c r="J34" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="K33" s="36" t="s">
+      <c r="K34" s="36" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A34" s="34" t="s">
+    <row r="35" spans="1:11" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A35" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="B34" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="68"/>
-      <c r="D34" s="35" t="s">
+      <c r="B35" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="52"/>
+      <c r="D35" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="E34" s="36" t="s">
+      <c r="E35" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="F34" s="36" t="s">
+      <c r="F35" s="36" t="s">
         <v>209</v>
       </c>
-      <c r="G34" s="36" t="s">
+      <c r="G35" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="H34" s="35" t="s">
+      <c r="H35" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="I34" s="36" t="s">
+      <c r="I35" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="J34" s="36" t="s">
+      <c r="J35" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="K34" s="36" t="s">
+      <c r="K35" s="36" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A35" s="34" t="s">
+    <row r="36" spans="1:11" s="7" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A36" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="B35" s="68" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="68"/>
-      <c r="D35" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="E35" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="F35" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="G35" s="36" t="s">
-        <v>234</v>
-      </c>
-      <c r="H35" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="I35" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="J35" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="K35" s="36" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A36" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="B36" s="69" t="s">
+      <c r="B36" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="69"/>
+      <c r="C36" s="57"/>
       <c r="D36" s="37"/>
       <c r="E36" s="38"/>
       <c r="F36" s="39"/>
@@ -2598,158 +2600,170 @@
       <c r="J36" s="39"/>
       <c r="K36" s="17"/>
     </row>
-    <row r="37" spans="1:11" s="7" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:11" s="7" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="B37" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="52"/>
+      <c r="D37" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="E37" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="F37" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="G37" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="H37" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="I37" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="J37" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="K37" s="36" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="34" t="s">
         <v>273</v>
       </c>
-      <c r="B37" s="68" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="68"/>
-      <c r="D37" s="20" t="s">
+      <c r="B38" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="52"/>
+      <c r="D38" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="E37" s="36" t="s">
+      <c r="E38" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="F37" s="36" t="s">
+      <c r="F38" s="36" t="s">
         <v>211</v>
       </c>
-      <c r="G37" s="36" t="s">
+      <c r="G38" s="36" t="s">
         <v>235</v>
       </c>
-      <c r="H37" s="35" t="s">
+      <c r="H38" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="I37" s="36" t="s">
+      <c r="I38" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="J37" s="36" t="s">
+      <c r="J38" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="K37" s="36" t="s">
+      <c r="K38" s="36" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="34" t="s">
+    <row r="39" spans="1:11" s="7" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="40" t="s">
         <v>274</v>
       </c>
-      <c r="B38" s="70" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" s="68"/>
-      <c r="D38" s="20" t="s">
+      <c r="B39" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="C39" s="54"/>
+      <c r="D39" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="E38" s="36" t="s">
+      <c r="E39" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="F38" s="36" t="s">
+      <c r="F39" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="G38" s="36" t="s">
+      <c r="G39" s="41" t="s">
         <v>236</v>
       </c>
-      <c r="H38" s="35" t="s">
+      <c r="H39" s="42" t="s">
         <v>146</v>
       </c>
-      <c r="I38" s="36" t="s">
+      <c r="I39" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="J38" s="36" t="s">
+      <c r="J39" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="K38" s="36" t="s">
+      <c r="K39" s="41" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="7" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="40" t="s">
-        <v>275</v>
-      </c>
-      <c r="B39" s="71" t="s">
+    <row r="40" spans="1:11" s="7" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="71"/>
-      <c r="D39" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="E39" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>213</v>
-      </c>
-      <c r="G39" s="41" t="s">
-        <v>237</v>
-      </c>
-      <c r="H39" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="I39" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="J39" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="K39" s="41" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" s="7" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="72"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="55"/>
+      <c r="K40" s="55"/>
     </row>
     <row r="41" spans="1:11" s="30" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C41" s="25"/>
       <c r="D41" s="23"/>
       <c r="E41" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F41" s="23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G41" s="27"/>
       <c r="H41" s="28"/>
       <c r="I41" s="29"/>
       <c r="J41" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:C8"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
@@ -2762,36 +2776,24 @@
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:C8"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:F4"/>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B4:C4">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:F4" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B4:C4" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"--,01-银行非保本理财,02-信托公司资管产品,03-证券公司及其子公司资管产品,04-基金管理公司及其子公司专户,05-期货公司及其子公司资管产品,06-保险资管产品,07-金融资产投资公司资管产品,08-公募基金"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D4">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D4" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
